--- a/sheets/민요/검수/창부타령 2.xlsx
+++ b/sheets/민요/검수/창부타령 2.xlsx
@@ -405,7 +405,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -545,13 +545,13 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|―</t>
+          <t xml:space="preserve">–|–</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―</t>
+          <t xml:space="preserve">–
+–</t>
         </is>
       </c>
       <c r="I2" s="2"/>
@@ -656,12 +656,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="I5" s="2"/>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I17" s="2"/>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|湳</t>
+          <t xml:space="preserve">–|湳</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 湳</t>
         </is>
       </c>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1319,13 +1319,13 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳湳|―</t>
+          <t xml:space="preserve">湳湳|–</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">湳湳
-―</t>
+–</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1359,12 +1359,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I23" s="2"/>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I25" s="2"/>
@@ -1695,13 +1695,13 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌|―</t>
+          <t xml:space="preserve">㴌|–</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-―</t>
+–</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -1735,12 +1735,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I33" s="2"/>
@@ -1770,12 +1770,12 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|湳</t>
+          <t xml:space="preserve">–|湳</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 湳</t>
         </is>
       </c>
@@ -2232,13 +2232,13 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2386,13 +2386,13 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―</t>
+          <t xml:space="preserve">潢|–</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2426,12 +2426,12 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I51" s="2"/>
@@ -2461,12 +2461,12 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無|南</t>
+          <t xml:space="preserve">–無|南</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無
+          <t xml:space="preserve">–無
 南</t>
         </is>
       </c>
@@ -2548,13 +2548,13 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無南</t>
+          <t xml:space="preserve">–|無南</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無南</t>
         </is>
       </c>
@@ -2860,13 +2860,13 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -2935,13 +2935,13 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―南</t>
+          <t xml:space="preserve">南|–南</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―南</t>
+–南</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3014,13 +3014,13 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―湳</t>
+          <t xml:space="preserve">南|–湳</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―湳</t>
+–湳</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無南</t>
+          <t xml:space="preserve">–|無南</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無南</t>
         </is>
       </c>
@@ -3485,13 +3485,13 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|㳞</t>
+          <t xml:space="preserve">–|㳞</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㳞</t>
         </is>
       </c>
@@ -3683,12 +3683,12 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4305,12 +4305,12 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -4585,12 +4585,12 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|南</t>
+          <t xml:space="preserve">–|南</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -4747,13 +4747,13 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
@@ -4901,12 +4901,12 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|㴌</t>
+          <t xml:space="preserve">–|㴌</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
@@ -5099,12 +5099,12 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -5179,12 +5179,12 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I121" s="2"/>
@@ -5329,12 +5329,12 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       <c r="H3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―南</t>
+–南</t>
         </is>
       </c>
       <c r="I3" s="8" t="inlineStr">
@@ -5533,7 +5533,7 @@
       <c r="L3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-―</t>
+–</t>
         </is>
       </c>
       <c r="M3" s="8" t="inlineStr">
@@ -5554,8 +5554,8 @@
       </c>
       <c r="P3" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―</t>
+          <t xml:space="preserve">–
+–</t>
         </is>
       </c>
       <c r="Q3" s="8"/>
@@ -5614,13 +5614,13 @@
       </c>
       <c r="L4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M4" s="9"/>
       <c r="N4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O4" s="9"/>
@@ -5635,7 +5635,7 @@
       <c r="A5" s="0"/>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㳞</t>
         </is>
       </c>
@@ -5665,7 +5665,7 @@
       <c r="H5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―湳</t>
+–湳</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
@@ -5676,7 +5676,7 @@
       <c r="J5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="K5" s="9" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="L5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 湳</t>
         </is>
       </c>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="N5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 湳</t>
         </is>
       </c>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -5759,7 +5759,7 @@
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K6" s="10"/>
@@ -5785,7 +5785,7 @@
       </c>
       <c r="P6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="Q6" s="10"/>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="J7" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無
+          <t xml:space="preserve">–無
 南</t>
         </is>
       </c>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="N8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O8" s="9" t="inlineStr">
@@ -6013,7 +6013,7 @@
       <c r="J9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="K9" s="9" t="inlineStr">
@@ -6035,7 +6035,7 @@
       <c r="N9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">湳湳
-―</t>
+–</t>
         </is>
       </c>
       <c r="O9" s="9" t="inlineStr">
@@ -6059,7 +6059,7 @@
       <c r="A10" s="0"/>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -6105,7 +6105,7 @@
       <c r="M10" s="10"/>
       <c r="N10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O10" s="10"/>
@@ -6215,7 +6215,7 @@
       <c r="A12" s="0"/>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C12" s="9"/>
@@ -6263,7 +6263,7 @@
       <c r="M12" s="9"/>
       <c r="N12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O12" s="9"/>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -6315,7 +6315,7 @@
       </c>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無南</t>
         </is>
       </c>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無南</t>
         </is>
       </c>
@@ -6527,7 +6527,7 @@
       <c r="A16" s="0"/>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -6614,7 +6614,7 @@
       <c r="D17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -6636,7 +6636,7 @@
       <c r="H17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
@@ -6647,7 +6647,7 @@
       <c r="J17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr">
@@ -6658,7 +6658,7 @@
       <c r="L17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="M17" s="9" t="inlineStr">
@@ -6696,7 +6696,7 @@
       <c r="E18" s="10"/>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>

--- a/sheets/민요/검수/창부타령 2.xlsx
+++ b/sheets/민요/검수/창부타령 2.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5452,267 +5493,267 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">창부타령 2</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">버림</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞㴌
 潢</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">모진</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">청송</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –南</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">얼씨</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞㴌
 潢</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">실초</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 –</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">대</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 湳</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">나목</t>
         </is>
       </c>
-      <c r="P3" s="17" t="inlineStr">
+      <c r="P3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –</t>
         </is>
       </c>
-      <c r="Q3" s="8"/>
+      <c r="Q3" s="22"/>
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">손</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">간</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M4" s="9"/>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="M4" s="25"/>
+      <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O4" s="9"/>
-      <c r="P4" s="17" t="inlineStr">
+      <c r="O4" s="25"/>
+      <c r="P4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞㴌</t>
         </is>
       </c>
-      <c r="Q4" s="9"/>
+      <c r="Q4" s="25"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="C5" s="25"/>
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">으로</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 㳞</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">히</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –湳</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="I5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">절시</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="K5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">장</t>
         </is>
       </c>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 湳</t>
         </is>
       </c>
-      <c r="M5" s="9" t="inlineStr">
+      <c r="M5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">장</t>
         </is>
       </c>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 湳</t>
         </is>
       </c>
-      <c r="O5" s="9" t="inlineStr">
+      <c r="O5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">먹</t>
         </is>
       </c>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞㴌
 潢</t>
         </is>
       </c>
-      <c r="Q5" s="9" t="inlineStr">
+      <c r="Q5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">버리</t>
         </is>
@@ -5720,162 +5761,162 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">온</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">호</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="G6" s="27"/>
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞㴌</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K6" s="10"/>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="K6" s="27"/>
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞㴌</t>
         </is>
       </c>
-      <c r="M6" s="10" t="inlineStr">
+      <c r="M6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
       </c>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="O6" s="10" t="inlineStr">
+      <c r="O6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="P6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="Q6" s="10"/>
+      <c r="Q6" s="27"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">쓰라</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無南</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꺽어</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">떨어</t>
         </is>
       </c>
-      <c r="H7" s="18" t="inlineStr">
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞㴌
 潢</t>
         </is>
       </c>
-      <c r="I7" s="11" t="inlineStr">
+      <c r="I7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">지화자</t>
         </is>
       </c>
-      <c r="J7" s="18" t="inlineStr">
+      <c r="J7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–無
 南</t>
         </is>
       </c>
-      <c r="K7" s="11" t="inlineStr">
+      <c r="K7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">앙</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞㴌
 潢無</t>
         </is>
       </c>
-      <c r="M7" s="8" t="inlineStr">
+      <c r="M7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">살림</t>
         </is>
       </c>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
 湳</t>
         </is>
       </c>
-      <c r="O7" s="8" t="inlineStr">
+      <c r="O7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">물</t>
         </is>
       </c>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無南</t>
         </is>
       </c>
-      <c r="Q7" s="8" t="inlineStr">
+      <c r="Q7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">시에</t>
         </is>
@@ -5883,82 +5924,82 @@
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞㴌</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">어하</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞㴌</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">진</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="I8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J8" s="18" t="inlineStr">
+      <c r="J8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="K8" s="12" t="inlineStr">
+      <c r="K8" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">벗은</t>
         </is>
       </c>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M8" s="9" t="inlineStr">
+      <c r="M8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">살</t>
         </is>
       </c>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O8" s="9" t="inlineStr">
+      <c r="O8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">마</t>
         </is>
       </c>
-      <c r="P8" s="17" t="inlineStr">
+      <c r="P8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="Q8" s="9" t="inlineStr">
+      <c r="Q8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -5966,90 +6007,90 @@
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無
 南</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">거든</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無南</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">다가</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無南</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃을</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無南</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="I9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">좋네</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="K9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">설</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南
 仲姑</t>
         </is>
       </c>
-      <c r="M9" s="9" t="inlineStr">
+      <c r="M9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">이가</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="N9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳湳
 –</t>
         </is>
       </c>
-      <c r="O9" s="9" t="inlineStr">
+      <c r="O9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">시고</t>
         </is>
       </c>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 㴌湳</t>
         </is>
       </c>
-      <c r="Q9" s="9" t="inlineStr">
+      <c r="Q9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">너</t>
         </is>
@@ -6057,64 +6098,64 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="27"/>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="18" t="inlineStr">
+      <c r="G10" s="27"/>
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑
 ‹</t>
         </is>
       </c>
-      <c r="I10" s="13"/>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="I10" s="26"/>
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K10" s="10" t="inlineStr">
+      <c r="K10" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">움</t>
         </is>
       </c>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M10" s="10"/>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="M10" s="27"/>
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O10" s="10"/>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="O10" s="27"/>
+      <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞㴌</t>
         </is>
       </c>
-      <c r="Q10" s="10" t="inlineStr">
+      <c r="Q10" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
@@ -6122,90 +6163,90 @@
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 湳仲</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">시들</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㳞㴌</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">낙화</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無
 南</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아니노</t>
         </is>
       </c>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr">
+      <c r="K11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">부모</t>
         </is>
       </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌湳
 㳞㴌</t>
         </is>
       </c>
-      <c r="M11" s="8" t="inlineStr">
+      <c r="M11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">요만</t>
         </is>
       </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 湳㳞</t>
         </is>
       </c>
-      <c r="O11" s="8" t="inlineStr">
+      <c r="O11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">팔을</t>
         </is>
       </c>
-      <c r="P11" s="18" t="inlineStr">
+      <c r="P11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞㴌
 潢</t>
         </is>
       </c>
-      <c r="Q11" s="11" t="inlineStr">
+      <c r="Q11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">쫓아</t>
         </is>
@@ -6213,66 +6254,66 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="C12" s="25"/>
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I12" s="9"/>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="I12" s="25"/>
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K12" s="9" t="inlineStr">
+      <c r="K12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">생</t>
         </is>
       </c>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞㴌</t>
         </is>
       </c>
-      <c r="M12" s="9"/>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="M12" s="25"/>
+      <c r="N12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O12" s="9"/>
-      <c r="P12" s="17" t="inlineStr">
+      <c r="O12" s="25"/>
+      <c r="P12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="Q12" s="9" t="inlineStr">
+      <c r="Q12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
@@ -6280,90 +6321,90 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌湳</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">심코</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">전</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">진다</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無南</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">지는</t>
         </is>
       </c>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無南</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">각이</t>
         </is>
       </c>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無南</t>
         </is>
       </c>
-      <c r="M13" s="9" t="inlineStr">
+      <c r="M13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">하면</t>
         </is>
       </c>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㳞㴌</t>
         </is>
       </c>
-      <c r="O13" s="9" t="inlineStr">
+      <c r="O13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">베고</t>
         </is>
       </c>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
 無南</t>
         </is>
       </c>
-      <c r="Q13" s="9" t="inlineStr">
+      <c r="Q13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">예</t>
         </is>
@@ -6371,62 +6412,62 @@
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞㴌</t>
         </is>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="27"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞㴌</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="I14" s="27"/>
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="K14" s="27"/>
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="17" t="inlineStr">
+      <c r="M14" s="27"/>
+      <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞㴌</t>
         </is>
       </c>
-      <c r="O14" s="10"/>
-      <c r="P14" s="17" t="inlineStr">
+      <c r="O14" s="27"/>
+      <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="Q14" s="10" t="inlineStr">
+      <c r="Q14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">왔</t>
         </is>
@@ -6434,90 +6475,90 @@
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞㴌
 潢</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">밟고</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
 仲姑</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">내버</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞㴌
 潢</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">서러</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南
 仲姑</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="I15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">못하</t>
         </is>
       </c>
-      <c r="J15" s="17" t="inlineStr">
+      <c r="J15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南
 仲姑</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr">
+      <c r="K15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">절로</t>
         </is>
       </c>
-      <c r="L15" s="17" t="inlineStr">
+      <c r="L15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南
 仲姑</t>
         </is>
       </c>
-      <c r="M15" s="8" t="inlineStr">
+      <c r="M15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">넉넉</t>
         </is>
       </c>
-      <c r="N15" s="17" t="inlineStr">
+      <c r="N15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無南</t>
         </is>
       </c>
-      <c r="O15" s="8" t="inlineStr">
+      <c r="O15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">누웠</t>
         </is>
       </c>
-      <c r="P15" s="17" t="inlineStr">
+      <c r="P15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="Q15" s="8" t="inlineStr">
+      <c r="Q15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">노라</t>
         </is>
@@ -6525,209 +6566,209 @@
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="G16" s="9" t="inlineStr">
+      <c r="G16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">워</t>
         </is>
       </c>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
+      <c r="I16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="J16" s="17" t="inlineStr">
+      <c r="J16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K16" s="9" t="inlineStr">
+      <c r="K16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">난</t>
         </is>
       </c>
-      <c r="L16" s="17" t="inlineStr">
+      <c r="L16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M16" s="9" t="inlineStr">
+      <c r="M16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">한</t>
         </is>
       </c>
-      <c r="N16" s="17" t="inlineStr">
+      <c r="N16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="O16" s="9"/>
-      <c r="P16" s="17" t="inlineStr">
+      <c r="O16" s="25"/>
+      <c r="P16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q16" s="9"/>
+      <c r="Q16" s="25"/>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無南</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">가니</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南^</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="G17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">마라</t>
         </is>
       </c>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="I17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="J17" s="17" t="inlineStr">
+      <c r="J17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="K17" s="9" t="inlineStr">
+      <c r="K17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="L17" s="17" t="inlineStr">
+      <c r="L17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="M17" s="9" t="inlineStr">
+      <c r="M17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="N17" s="17" t="inlineStr">
+      <c r="N17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無南</t>
         </is>
       </c>
-      <c r="O17" s="9" t="inlineStr">
+      <c r="O17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">으니</t>
         </is>
       </c>
-      <c r="P17" s="17"/>
-      <c r="Q17" s="9"/>
+      <c r="P17" s="21"/>
+      <c r="Q17" s="25"/>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="C18" s="27"/>
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E18" s="10"/>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="E18" s="27"/>
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="G18" s="27"/>
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I18" s="10"/>
-      <c r="J18" s="17" t="inlineStr">
+      <c r="I18" s="27"/>
+      <c r="J18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K18" s="10"/>
-      <c r="L18" s="17" t="inlineStr">
+      <c r="K18" s="27"/>
+      <c r="L18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M18" s="10"/>
-      <c r="N18" s="17" t="inlineStr">
+      <c r="M18" s="27"/>
+      <c r="N18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑
 △</t>
         </is>
       </c>
-      <c r="O18" s="10"/>
-      <c r="P18" s="17"/>
-      <c r="Q18" s="10"/>
+      <c r="O18" s="27"/>
+      <c r="P18" s="21"/>
+      <c r="Q18" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/창부타령 2.xlsx
+++ b/sheets/민요/검수/창부타령 2.xlsx
@@ -5470,28 +5470,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="60.41" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="60.41" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="60.41" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="Q4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="60.41" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="60.41" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
       </c>
       <c r="Q6" s="27"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="60.41" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="60.41" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="60.41" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="60.41" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="60.41" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="23" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="60.41" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="60.41" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="60.41" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="60.41" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="60.41" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="Q16" s="25"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="60.41" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
       <c r="P17" s="21"/>
       <c r="Q17" s="25"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="60.41" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>

--- a/sheets/민요/검수/창부타령 2.xlsx
+++ b/sheets/민요/검수/창부타령 2.xlsx
@@ -3257,13 +3257,12 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲姑|‹</t>
+          <t xml:space="preserve">仲姑</t>
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲姑
-‹</t>
+          <t xml:space="preserve">仲姑</t>
         </is>
       </c>
       <c r="I71" s="3"/>
@@ -6123,8 +6122,7 @@
       <c r="G10" s="27"/>
       <c r="H10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲姑
-‹</t>
+          <t xml:space="preserve">仲姑</t>
         </is>
       </c>
       <c r="I10" s="26"/>

--- a/sheets/민요/검수/창부타령 2.xlsx
+++ b/sheets/민요/검수/창부타령 2.xlsx
@@ -5523,7 +5523,8 @@
       </c>
       <c r="C3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">버림</t>
+          <t xml:space="preserve">버
+림</t>
         </is>
       </c>
       <c r="D3" s="21" t="inlineStr">
@@ -5534,7 +5535,8 @@
       </c>
       <c r="E3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">모진</t>
+          <t xml:space="preserve">모
+진</t>
         </is>
       </c>
       <c r="F3" s="23" t="inlineStr">
@@ -5545,7 +5547,8 @@
       </c>
       <c r="G3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">청송</t>
+          <t xml:space="preserve">청
+송</t>
         </is>
       </c>
       <c r="H3" s="21" t="inlineStr">
@@ -5556,7 +5559,8 @@
       </c>
       <c r="I3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">얼씨</t>
+          <t xml:space="preserve">얼
+씨</t>
         </is>
       </c>
       <c r="J3" s="21" t="inlineStr">
@@ -5567,7 +5571,8 @@
       </c>
       <c r="K3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">실초</t>
+          <t xml:space="preserve">실
+초</t>
         </is>
       </c>
       <c r="L3" s="21" t="inlineStr">
@@ -5589,7 +5594,8 @@
       </c>
       <c r="O3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">나목</t>
+          <t xml:space="preserve">나
+목</t>
         </is>
       </c>
       <c r="P3" s="21" t="inlineStr">
@@ -5688,7 +5694,8 @@
       </c>
       <c r="E5" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">으로</t>
+          <t xml:space="preserve">으
+로</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr">
@@ -5710,7 +5717,8 @@
       </c>
       <c r="I5" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">절시</t>
+          <t xml:space="preserve">절
+시</t>
         </is>
       </c>
       <c r="J5" s="21" t="inlineStr">
@@ -5754,7 +5762,8 @@
       </c>
       <c r="Q5" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">버리</t>
+          <t xml:space="preserve">버
+리</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5849,8 @@
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">쓰라</t>
+          <t xml:space="preserve">쓰
+라</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -5851,7 +5861,8 @@
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">꺽어</t>
+          <t xml:space="preserve">꺽
+어</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
@@ -5862,7 +5873,8 @@
       </c>
       <c r="G7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">떨어</t>
+          <t xml:space="preserve">떨
+어</t>
         </is>
       </c>
       <c r="H7" s="23" t="inlineStr">
@@ -5873,7 +5885,9 @@
       </c>
       <c r="I7" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">지화자</t>
+          <t xml:space="preserve">지
+화
+자</t>
         </is>
       </c>
       <c r="J7" s="23" t="inlineStr">
@@ -5895,7 +5909,8 @@
       </c>
       <c r="M7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">살림</t>
+          <t xml:space="preserve">살
+림</t>
         </is>
       </c>
       <c r="N7" s="21" t="inlineStr">
@@ -5917,7 +5932,8 @@
       </c>
       <c r="Q7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">시에</t>
+          <t xml:space="preserve">시
+에</t>
         </is>
       </c>
     </row>
@@ -5940,7 +5956,8 @@
       </c>
       <c r="E8" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">어하</t>
+          <t xml:space="preserve">어
+하</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr">
@@ -5970,7 +5987,8 @@
       </c>
       <c r="K8" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">벗은</t>
+          <t xml:space="preserve">벗
+은</t>
         </is>
       </c>
       <c r="L8" s="21" t="inlineStr">
@@ -6014,7 +6032,8 @@
       </c>
       <c r="C9" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">거든</t>
+          <t xml:space="preserve">거
+든</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -6025,7 +6044,8 @@
       </c>
       <c r="E9" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">다가</t>
+          <t xml:space="preserve">다
+가</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -6036,7 +6056,8 @@
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">꽃을</t>
+          <t xml:space="preserve">꽃
+을</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -6047,7 +6068,8 @@
       </c>
       <c r="I9" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">좋네</t>
+          <t xml:space="preserve">좋
+네</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr">
@@ -6069,7 +6091,8 @@
       </c>
       <c r="M9" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">이가</t>
+          <t xml:space="preserve">이
+가</t>
         </is>
       </c>
       <c r="N9" s="21" t="inlineStr">
@@ -6080,7 +6103,8 @@
       </c>
       <c r="O9" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">시고</t>
+          <t xml:space="preserve">시
+고</t>
         </is>
       </c>
       <c r="P9" s="21" t="inlineStr">
@@ -6180,7 +6204,8 @@
       </c>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">시들</t>
+          <t xml:space="preserve">시
+들</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -6191,7 +6216,8 @@
       </c>
       <c r="G11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">낙화</t>
+          <t xml:space="preserve">낙
+화</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -6202,7 +6228,9 @@
       </c>
       <c r="I11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">아니노</t>
+          <t xml:space="preserve">아
+니
+노</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
@@ -6213,7 +6241,8 @@
       </c>
       <c r="K11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">부모</t>
+          <t xml:space="preserve">부
+모</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
@@ -6224,7 +6253,8 @@
       </c>
       <c r="M11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">요만</t>
+          <t xml:space="preserve">요
+만</t>
         </is>
       </c>
       <c r="N11" s="21" t="inlineStr">
@@ -6235,7 +6265,8 @@
       </c>
       <c r="O11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">팔을</t>
+          <t xml:space="preserve">팔
+을</t>
         </is>
       </c>
       <c r="P11" s="23" t="inlineStr">
@@ -6246,7 +6277,8 @@
       </c>
       <c r="Q11" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">쫓아</t>
+          <t xml:space="preserve">쫓
+아</t>
         </is>
       </c>
     </row>
@@ -6327,7 +6359,8 @@
       </c>
       <c r="C13" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">심코</t>
+          <t xml:space="preserve">심
+코</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -6349,7 +6382,8 @@
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">진다</t>
+          <t xml:space="preserve">진
+다</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -6360,7 +6394,8 @@
       </c>
       <c r="I13" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">지는</t>
+          <t xml:space="preserve">지
+는</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr">
@@ -6371,7 +6406,8 @@
       </c>
       <c r="K13" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">각이</t>
+          <t xml:space="preserve">각
+이</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -6382,7 +6418,8 @@
       </c>
       <c r="M13" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">하면</t>
+          <t xml:space="preserve">하
+면</t>
         </is>
       </c>
       <c r="N13" s="21" t="inlineStr">
@@ -6393,7 +6430,8 @@
       </c>
       <c r="O13" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">베고</t>
+          <t xml:space="preserve">베
+고</t>
         </is>
       </c>
       <c r="P13" s="21" t="inlineStr">
@@ -6481,7 +6519,8 @@
       </c>
       <c r="C15" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">밟고</t>
+          <t xml:space="preserve">밟
+고</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -6492,7 +6531,8 @@
       </c>
       <c r="E15" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">내버</t>
+          <t xml:space="preserve">내
+버</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -6503,7 +6543,8 @@
       </c>
       <c r="G15" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">서러</t>
+          <t xml:space="preserve">서
+러</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -6514,7 +6555,8 @@
       </c>
       <c r="I15" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">못하</t>
+          <t xml:space="preserve">못
+하</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr">
@@ -6525,7 +6567,8 @@
       </c>
       <c r="K15" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">절로</t>
+          <t xml:space="preserve">절
+로</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -6536,7 +6579,8 @@
       </c>
       <c r="M15" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">넉넉</t>
+          <t xml:space="preserve">넉
+넉</t>
         </is>
       </c>
       <c r="N15" s="21" t="inlineStr">
@@ -6547,7 +6591,8 @@
       </c>
       <c r="O15" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">누웠</t>
+          <t xml:space="preserve">누
+웠</t>
         </is>
       </c>
       <c r="P15" s="21" t="inlineStr">
@@ -6558,7 +6603,8 @@
       </c>
       <c r="Q15" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">노라</t>
+          <t xml:space="preserve">노
+라</t>
         </is>
       </c>
     </row>
@@ -6647,7 +6693,8 @@
       </c>
       <c r="C17" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">가니</t>
+          <t xml:space="preserve">가
+니</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -6669,7 +6716,8 @@
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">마라</t>
+          <t xml:space="preserve">마
+라</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
@@ -6713,7 +6761,8 @@
       </c>
       <c r="O17" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">으니</t>
+          <t xml:space="preserve">으
+니</t>
         </is>
       </c>
       <c r="P17" s="21"/>

--- a/sheets/민요/검수/창부타령 2.xlsx
+++ b/sheets/민요/검수/창부타령 2.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,6 +241,24 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5521,7 +5544,7 @@
 㳞</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">버
 림</t>
@@ -5533,7 +5556,7 @@
 潢</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">모
 진</t>
@@ -5545,7 +5568,7 @@
 㳞</t>
         </is>
       </c>
-      <c r="G3" s="24" t="inlineStr">
+      <c r="G3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">청
 송</t>
@@ -5557,7 +5580,7 @@
 –南</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">얼
 씨</t>
@@ -5569,7 +5592,7 @@
 潢</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
+      <c r="K3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">실
 초</t>
@@ -5581,7 +5604,7 @@
 –</t>
         </is>
       </c>
-      <c r="M3" s="22" t="inlineStr">
+      <c r="M3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">대</t>
         </is>
@@ -5592,7 +5615,7 @@
 湳</t>
         </is>
       </c>
-      <c r="O3" s="22" t="inlineStr">
+      <c r="O3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">나
 목</t>
@@ -5604,7 +5627,7 @@
 –</t>
         </is>
       </c>
-      <c r="Q3" s="22"/>
+      <c r="Q3" s="29"/>
     </row>
     <row r="4" ht="60.41" customHeight="1">
       <c r="A4" s="0"/>
@@ -5613,7 +5636,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
@@ -5623,7 +5646,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">손</t>
         </is>
@@ -5633,7 +5656,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G4" s="25" t="inlineStr">
+      <c r="G4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -5643,7 +5666,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I4" s="25" t="inlineStr">
+      <c r="I4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -5653,7 +5676,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K4" s="25" t="inlineStr">
+      <c r="K4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">간</t>
         </is>
@@ -5663,19 +5686,19 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M4" s="25"/>
+      <c r="M4" s="31"/>
       <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O4" s="25"/>
+      <c r="O4" s="31"/>
       <c r="P4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞㴌</t>
         </is>
       </c>
-      <c r="Q4" s="25"/>
+      <c r="Q4" s="31"/>
     </row>
     <row r="5" ht="60.41" customHeight="1">
       <c r="A5" s="0"/>
@@ -5685,14 +5708,14 @@
 㴌</t>
         </is>
       </c>
-      <c r="C5" s="25"/>
+      <c r="C5" s="31"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">으
 로</t>
@@ -5704,7 +5727,7 @@
 㳞</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">히</t>
         </is>
@@ -5715,7 +5738,7 @@
 –湳</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">절
 시</t>
@@ -5727,7 +5750,7 @@
 –</t>
         </is>
       </c>
-      <c r="K5" s="25" t="inlineStr">
+      <c r="K5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">장</t>
         </is>
@@ -5738,7 +5761,7 @@
 湳</t>
         </is>
       </c>
-      <c r="M5" s="25" t="inlineStr">
+      <c r="M5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">장</t>
         </is>
@@ -5749,7 +5772,7 @@
 湳</t>
         </is>
       </c>
-      <c r="O5" s="25" t="inlineStr">
+      <c r="O5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">먹</t>
         </is>
@@ -5760,7 +5783,7 @@
 潢</t>
         </is>
       </c>
-      <c r="Q5" s="25" t="inlineStr">
+      <c r="Q5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">버
 리</t>
@@ -5774,7 +5797,7 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">온</t>
         </is>
@@ -5784,7 +5807,7 @@
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="E6" s="27" t="inlineStr">
+      <c r="E6" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">호</t>
         </is>
@@ -5795,13 +5818,13 @@
 △</t>
         </is>
       </c>
-      <c r="G6" s="27"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞㴌</t>
         </is>
       </c>
-      <c r="I6" s="27" t="inlineStr">
+      <c r="I6" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -5811,13 +5834,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K6" s="27"/>
+      <c r="K6" s="33"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞㴌</t>
         </is>
       </c>
-      <c r="M6" s="27" t="inlineStr">
+      <c r="M6" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
@@ -5827,7 +5850,7 @@
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="O6" s="27" t="inlineStr">
+      <c r="O6" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -5837,7 +5860,7 @@
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="Q6" s="27"/>
+      <c r="Q6" s="33"/>
     </row>
     <row r="7" ht="60.41" customHeight="1">
       <c r="A7" s="0"/>
@@ -5847,7 +5870,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">쓰
 라</t>
@@ -5859,7 +5882,7 @@
 無南</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">꺽
 어</t>
@@ -5871,7 +5894,7 @@
 㳞</t>
         </is>
       </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="G7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">떨
 어</t>
@@ -5883,7 +5906,7 @@
 潢</t>
         </is>
       </c>
-      <c r="I7" s="24" t="inlineStr">
+      <c r="I7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">지
 화
@@ -5896,7 +5919,7 @@
 南</t>
         </is>
       </c>
-      <c r="K7" s="24" t="inlineStr">
+      <c r="K7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">앙</t>
         </is>
@@ -5907,7 +5930,7 @@
 潢無</t>
         </is>
       </c>
-      <c r="M7" s="22" t="inlineStr">
+      <c r="M7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">살
 림</t>
@@ -5919,7 +5942,7 @@
 湳</t>
         </is>
       </c>
-      <c r="O7" s="22" t="inlineStr">
+      <c r="O7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">물</t>
         </is>
@@ -5930,7 +5953,7 @@
 無南</t>
         </is>
       </c>
-      <c r="Q7" s="22" t="inlineStr">
+      <c r="Q7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">시
 에</t>
@@ -5944,7 +5967,7 @@
           <t xml:space="preserve">㳞㴌</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -5954,7 +5977,7 @@
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="E8" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">어
 하</t>
@@ -5965,7 +5988,7 @@
           <t xml:space="preserve">㳞㴌</t>
         </is>
       </c>
-      <c r="G8" s="25" t="inlineStr">
+      <c r="G8" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">진</t>
         </is>
@@ -5975,7 +5998,7 @@
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="I8" s="25" t="inlineStr">
+      <c r="I8" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5985,7 +6008,7 @@
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="K8" s="28" t="inlineStr">
+      <c r="K8" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">벗
 은</t>
@@ -5996,7 +6019,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M8" s="25" t="inlineStr">
+      <c r="M8" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">살</t>
         </is>
@@ -6006,7 +6029,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O8" s="25" t="inlineStr">
+      <c r="O8" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">마</t>
         </is>
@@ -6016,7 +6039,7 @@
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="Q8" s="25" t="inlineStr">
+      <c r="Q8" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -6030,7 +6053,7 @@
 南</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">거
 든</t>
@@ -6042,7 +6065,7 @@
 無南</t>
         </is>
       </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">다
 가</t>
@@ -6054,7 +6077,7 @@
 無南</t>
         </is>
       </c>
-      <c r="G9" s="25" t="inlineStr">
+      <c r="G9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃
 을</t>
@@ -6066,7 +6089,7 @@
 無南</t>
         </is>
       </c>
-      <c r="I9" s="25" t="inlineStr">
+      <c r="I9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">좋
 네</t>
@@ -6078,7 +6101,7 @@
 –</t>
         </is>
       </c>
-      <c r="K9" s="25" t="inlineStr">
+      <c r="K9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">설</t>
         </is>
@@ -6089,7 +6112,7 @@
 仲姑</t>
         </is>
       </c>
-      <c r="M9" s="25" t="inlineStr">
+      <c r="M9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">이
 가</t>
@@ -6101,7 +6124,7 @@
 –</t>
         </is>
       </c>
-      <c r="O9" s="25" t="inlineStr">
+      <c r="O9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">시
 고</t>
@@ -6113,7 +6136,7 @@
 㴌湳</t>
         </is>
       </c>
-      <c r="Q9" s="25" t="inlineStr">
+      <c r="Q9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">너</t>
         </is>
@@ -6127,13 +6150,13 @@
 △</t>
         </is>
       </c>
-      <c r="C10" s="27"/>
+      <c r="C10" s="33"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="E10" s="27" t="inlineStr">
+      <c r="E10" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
@@ -6143,19 +6166,19 @@
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="G10" s="27"/>
+      <c r="G10" s="33"/>
       <c r="H10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="I10" s="26"/>
+      <c r="I10" s="32"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K10" s="27" t="inlineStr">
+      <c r="K10" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">움</t>
         </is>
@@ -6165,19 +6188,19 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M10" s="27"/>
+      <c r="M10" s="33"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O10" s="27"/>
+      <c r="O10" s="33"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞㴌</t>
         </is>
       </c>
-      <c r="Q10" s="27" t="inlineStr">
+      <c r="Q10" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
@@ -6191,7 +6214,7 @@
 湳仲</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
@@ -6202,7 +6225,7 @@
 南</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">시
 들</t>
@@ -6214,7 +6237,7 @@
 㳞㴌</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">낙
 화</t>
@@ -6226,7 +6249,7 @@
 南</t>
         </is>
       </c>
-      <c r="I11" s="22" t="inlineStr">
+      <c r="I11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 니
@@ -6239,7 +6262,7 @@
 南</t>
         </is>
       </c>
-      <c r="K11" s="22" t="inlineStr">
+      <c r="K11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">부
 모</t>
@@ -6251,7 +6274,7 @@
 㳞㴌</t>
         </is>
       </c>
-      <c r="M11" s="22" t="inlineStr">
+      <c r="M11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">요
 만</t>
@@ -6263,7 +6286,7 @@
 湳㳞</t>
         </is>
       </c>
-      <c r="O11" s="22" t="inlineStr">
+      <c r="O11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">팔
 을</t>
@@ -6275,7 +6298,7 @@
 潢</t>
         </is>
       </c>
-      <c r="Q11" s="24" t="inlineStr">
+      <c r="Q11" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">쫓
 아</t>
@@ -6289,13 +6312,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C12" s="25"/>
+      <c r="C12" s="31"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E12" s="25" t="inlineStr">
+      <c r="E12" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
@@ -6305,7 +6328,7 @@
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="G12" s="25" t="inlineStr">
+      <c r="G12" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -6315,13 +6338,13 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I12" s="25"/>
+      <c r="I12" s="31"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K12" s="25" t="inlineStr">
+      <c r="K12" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">생</t>
         </is>
@@ -6331,19 +6354,19 @@
           <t xml:space="preserve">㳞㴌</t>
         </is>
       </c>
-      <c r="M12" s="25"/>
+      <c r="M12" s="31"/>
       <c r="N12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O12" s="25"/>
+      <c r="O12" s="31"/>
       <c r="P12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="Q12" s="25" t="inlineStr">
+      <c r="Q12" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
@@ -6357,7 +6380,7 @@
 㴌湳</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">심
 코</t>
@@ -6369,7 +6392,7 @@
 南</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">전</t>
         </is>
@@ -6380,7 +6403,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="G13" s="25" t="inlineStr">
+      <c r="G13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">진
 다</t>
@@ -6392,7 +6415,7 @@
 無南</t>
         </is>
       </c>
-      <c r="I13" s="25" t="inlineStr">
+      <c r="I13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">지
 는</t>
@@ -6404,7 +6427,7 @@
 無南</t>
         </is>
       </c>
-      <c r="K13" s="25" t="inlineStr">
+      <c r="K13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">각
 이</t>
@@ -6416,7 +6439,7 @@
 無南</t>
         </is>
       </c>
-      <c r="M13" s="25" t="inlineStr">
+      <c r="M13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">하
 면</t>
@@ -6428,7 +6451,7 @@
 㳞㴌</t>
         </is>
       </c>
-      <c r="O13" s="25" t="inlineStr">
+      <c r="O13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">베
 고</t>
@@ -6440,7 +6463,7 @@
 無南</t>
         </is>
       </c>
-      <c r="Q13" s="25" t="inlineStr">
+      <c r="Q13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">예</t>
         </is>
@@ -6453,13 +6476,13 @@
           <t xml:space="preserve">㳞㴌</t>
         </is>
       </c>
-      <c r="C14" s="27"/>
+      <c r="C14" s="33"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="E14" s="27" t="inlineStr">
+      <c r="E14" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -6469,7 +6492,7 @@
           <t xml:space="preserve">㳞㴌</t>
         </is>
       </c>
-      <c r="G14" s="27" t="inlineStr">
+      <c r="G14" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -6479,31 +6502,31 @@
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="I14" s="27"/>
+      <c r="I14" s="33"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="K14" s="27"/>
+      <c r="K14" s="33"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="M14" s="27"/>
+      <c r="M14" s="33"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞㴌</t>
         </is>
       </c>
-      <c r="O14" s="27"/>
+      <c r="O14" s="33"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="Q14" s="27" t="inlineStr">
+      <c r="Q14" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">왔</t>
         </is>
@@ -6517,7 +6540,7 @@
 潢</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">밟
 고</t>
@@ -6529,7 +6552,7 @@
 仲姑</t>
         </is>
       </c>
-      <c r="E15" s="24" t="inlineStr">
+      <c r="E15" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">내
 버</t>
@@ -6541,7 +6564,7 @@
 潢</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="G15" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">서
 러</t>
@@ -6553,7 +6576,7 @@
 仲姑</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr">
+      <c r="I15" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">못
 하</t>
@@ -6565,7 +6588,7 @@
 仲姑</t>
         </is>
       </c>
-      <c r="K15" s="22" t="inlineStr">
+      <c r="K15" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">절
 로</t>
@@ -6577,7 +6600,7 @@
 仲姑</t>
         </is>
       </c>
-      <c r="M15" s="22" t="inlineStr">
+      <c r="M15" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">넉
 넉</t>
@@ -6589,7 +6612,7 @@
 無南</t>
         </is>
       </c>
-      <c r="O15" s="22" t="inlineStr">
+      <c r="O15" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">누
 웠</t>
@@ -6601,7 +6624,7 @@
 姑</t>
         </is>
       </c>
-      <c r="Q15" s="22" t="inlineStr">
+      <c r="Q15" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">노
 라</t>
@@ -6615,7 +6638,7 @@
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="C16" s="25" t="inlineStr">
+      <c r="C16" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
@@ -6625,7 +6648,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="E16" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -6635,7 +6658,7 @@
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="G16" s="25" t="inlineStr">
+      <c r="G16" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">워</t>
         </is>
@@ -6645,7 +6668,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I16" s="25" t="inlineStr">
+      <c r="I16" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -6655,7 +6678,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K16" s="25" t="inlineStr">
+      <c r="K16" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">난</t>
         </is>
@@ -6665,7 +6688,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M16" s="25" t="inlineStr">
+      <c r="M16" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">한</t>
         </is>
@@ -6675,13 +6698,13 @@
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="O16" s="25"/>
+      <c r="O16" s="31"/>
       <c r="P16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q16" s="25"/>
+      <c r="Q16" s="31"/>
     </row>
     <row r="17" ht="60.41" customHeight="1">
       <c r="A17" s="0"/>
@@ -6691,7 +6714,7 @@
 無南</t>
         </is>
       </c>
-      <c r="C17" s="25" t="inlineStr">
+      <c r="C17" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">가
 니</t>
@@ -6703,7 +6726,7 @@
 –</t>
         </is>
       </c>
-      <c r="E17" s="25" t="inlineStr">
+      <c r="E17" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
@@ -6714,7 +6737,7 @@
 南^</t>
         </is>
       </c>
-      <c r="G17" s="25" t="inlineStr">
+      <c r="G17" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">마
 라</t>
@@ -6726,7 +6749,7 @@
 –</t>
         </is>
       </c>
-      <c r="I17" s="25" t="inlineStr">
+      <c r="I17" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
@@ -6737,7 +6760,7 @@
 –</t>
         </is>
       </c>
-      <c r="K17" s="25" t="inlineStr">
+      <c r="K17" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -6748,7 +6771,7 @@
 –</t>
         </is>
       </c>
-      <c r="M17" s="25" t="inlineStr">
+      <c r="M17" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -6759,14 +6782,14 @@
 無南</t>
         </is>
       </c>
-      <c r="O17" s="25" t="inlineStr">
+      <c r="O17" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">으
 니</t>
         </is>
       </c>
       <c r="P17" s="21"/>
-      <c r="Q17" s="25"/>
+      <c r="Q17" s="31"/>
     </row>
     <row r="18" ht="60.41" customHeight="1">
       <c r="A18" s="0"/>
@@ -6775,47 +6798,47 @@
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="C18" s="27"/>
+      <c r="C18" s="33"/>
       <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E18" s="27"/>
+      <c r="E18" s="33"/>
       <c r="F18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="G18" s="27"/>
+      <c r="G18" s="33"/>
       <c r="H18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I18" s="27"/>
+      <c r="I18" s="33"/>
       <c r="J18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K18" s="27"/>
+      <c r="K18" s="33"/>
       <c r="L18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M18" s="27"/>
+      <c r="M18" s="33"/>
       <c r="N18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑
 △</t>
         </is>
       </c>
-      <c r="O18" s="27"/>
+      <c r="O18" s="33"/>
       <c r="P18" s="21"/>
-      <c r="Q18" s="27"/>
+      <c r="Q18" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/창부타령 2.xlsx
+++ b/sheets/민요/검수/창부타령 2.xlsx
@@ -65,10 +65,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="solid">

--- a/sheets/민요/검수/창부타령 2.xlsx
+++ b/sheets/민요/검수/창부타령 2.xlsx
@@ -3205,6 +3205,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -3225,10 +3228,10 @@
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="106.7" customHeight="1">
+    <row r="2" ht="68.97" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3251,7 +3254,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="106.7" customHeight="1">
+    <row r="3" ht="154.07" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3357,7 +3360,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="106.7" customHeight="1">
+    <row r="4" ht="154.07" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -3463,7 +3466,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="106.7" customHeight="1">
+    <row r="5" ht="154.07" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3579,7 +3582,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="106.7" customHeight="1">
+    <row r="6" ht="154.07" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3688,7 +3691,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="106.7" customHeight="1">
+    <row r="7" ht="154.07" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="23" t="inlineStr">
         <is>
@@ -3799,7 +3802,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="106.7" customHeight="1">
+    <row r="8" ht="154.07" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3908,7 +3911,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="106.7" customHeight="1">
+    <row r="9" ht="154.07" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="23" t="inlineStr">
         <is>
@@ -4021,7 +4024,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="106.7" customHeight="1">
+    <row r="10" ht="154.07" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4121,6 +4124,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="76"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="58"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/창부타령 2.xlsx
+++ b/sheets/민요/검수/창부타령 2.xlsx
@@ -3210,28 +3210,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="12" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="68.97" customHeight="true">
+    <row r="2" ht="64.52" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="154.07" customHeight="true">
+    <row r="3" ht="144.08" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="154.07" customHeight="true">
+    <row r="4" ht="144.08" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="154.07" customHeight="true">
+    <row r="5" ht="144.08" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="154.07" customHeight="true">
+    <row r="6" ht="144.08" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="154.07" customHeight="true">
+    <row r="7" ht="144.08" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="23" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="154.07" customHeight="true">
+    <row r="8" ht="144.08" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="154.07" customHeight="true">
+    <row r="9" ht="144.08" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="23" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="154.07" customHeight="true">
+    <row r="10" ht="144.08" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4124,6 +4124,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="58"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
 </worksheet>
 </file>